--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>A new offset or reverse-flow smoker trailer, 500-gallon class (wood, charcoal or pellets). Examples we read: Meadow Creek TS500 at $20,395 (webstaurantstore.com); Yoder Frontiersman at $8,495-$16,295 plus shipping (yodersmokers.com). The tow vehicle is YOUR pickup, at 0 in this plan. If you don't have one, budget a used pickup that tows at least 3,000 lb (1,360 kg): roughly 25,000-40,000 (Kit estimate).</t>
+          <t>A new offset or reverse-flow smoker trailer, 500-gallon class (wood, charcoal or pellets). Examples we read: Meadow Creek TS500 at $20,395 (webstaurantstore.com); Yoder Frontiersman at $8,495-$16,295 plus shipping (yodersmokers.com). The tow vehicle is YOUR pickup, at 0 in this plan. If you don't have one, budget a used pickup that tows at least 5,000 lb (2,270 kg), checked against the loaded trailer weight: roughly 25,000-40,000 (Kit estimate).</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="J19" s="35" t="inlineStr">
         <is>
-          <t>Average number of people working each event: about 1.5 on a drop-off, 3 on a staffed buffet, 4 on a full-service company event, 5 at a wedding and 4 on a live-fire booking (Kit estimate). Raise it for bigger events: the staffing sizes itself.</t>
+          <t>Average number of people working each event: about 1.5 on a drop-off, 3 on a staffed buffet for 70, 5 on a full-service company event, 7 at a wedding with the live pit (2 on the pit and 5 servers, as in the calculator's example) and 5 on a live-fire booking (Kit estimate). Weighted by the example mix in the Word plan, that averages about 3.4. Raise it for bigger events: the staffing sizes itself.</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="45" customHeight="1">
+    <row r="59" ht="59.75" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>Smoker yield</t>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D59" s="17" t="inlineStr">
         <is>
-          <t>Brisket and pork butt lose about half their weight in the smoker: 300 guests need roughly 200 lb (91 kg) of raw meat. Buy and cost by raw weight.</t>
+          <t>Brisket and pork butt lose about half their weight in the smoker: 300 guests need roughly 200 lb (91 kg) of raw meat at 1/3 lb cooked per guest; at the calculator's 8 oz, about 270 lb (123 kg). Buy and cost by raw weight.</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>Median hourly wages for restaurant cooks (35-2014), nonrestaurant food servers (35-3041) and chefs and head cooks (35-1011); 75th percentile $21.45 for cooks and $18.51 for servers. The plan pays the pit cook near the 75th percentile and the owner/pitmaster below the chefs and head cooks median: the rest comes from profit.</t>
+          <t>Mean hourly wages for restaurant cooks (35-2014) and nonrestaurant food servers (35-3041), and the median for chefs and head cooks (35-1011); 75th percentile $21.45 for cooks and $18.51 for servers. The plan pays the pit cook near the 75th percentile and the owner/pitmaster below the chefs and head cooks median: the rest comes from profit.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.033168571525444716</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (smoker trailer, smoker trailer upfit, used cargo van, van upfit and the plan review / trailer inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (smoker trailer, smoker trailer upfit, used cargo van, van upfit and the plan review / trailer inspection), not of the whole block: the other items are left out. No lender funds a build-out without a "&amp;"cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (smoker trailer, smoker trailer upfit, used cargo van, van upfit and the plan review / trailer inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>10511.428571428572</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital "&amp;"reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to 68971 of the 135671 total investment.</v>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
         <v>0.03</v>
       </c>
       <c r="F18" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra meat, ice, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (vehicle and trailer fuel, maintenance and registration are in row 27; wood, charcoal and propane are in row 15)","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra meat, ice, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (vehicle and trailer fuel, maintenance and registration are in row "&amp;"27; wood, charcoal and propane are in row 15)","")</f>
         <v>At 3% of sales: a cushion for unbudgeted event costs (extra meat, ice, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (vehicle and trailer fuel, maintenance and registration are in row 27; wood, charcoal and propane are in row 15)</v>
       </c>
       <c r="G18" s="68">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.033168571525444716</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (smoker trailer, smoker trailer upfit, used cargo van, van upfit and the plan review / trailer inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (smoker trailer, smoker trailer upfit, used cargo van, van upfit and the plan review / trailer inspection), not of the whole block: the other items are left out. No lender funds a build-out without a "&amp;"cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (smoker trailer, smoker trailer upfit, used cargo van, van upfit and the plan review / trailer inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>10511.428571428572</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital "&amp;"reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to 68971 of the 135671 total investment.</v>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
         <v>0.03</v>
       </c>
       <c r="F18" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra meat, ice, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (vehicle and trailer fuel, maintenance and registration are in row 27; wood, charcoal and propane are in row 15)","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra meat, ice, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (vehicle and trailer fuel, maintenance and registration are in row "&amp;"27; wood, charcoal and propane are in row 15)","")</f>
         <v>At 3% of sales: a cushion for unbudgeted event costs (extra meat, ice, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (vehicle and trailer fuel, maintenance and registration are in row 27; wood, charcoal and propane are in row 15)</v>
       </c>
       <c r="G18" s="68">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-financial-projections.xlsx
@@ -8236,7 +8236,7 @@
       <c r="N33" s="28" t="n"/>
       <c r="O33" s="28" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
